--- a/KURIKULUM2026_REVISI/024_MATRIKS_EKIVALENSI_KURIKULUM2025_KE_KURIKULUM2026.xlsx
+++ b/KURIKULUM2026_REVISI/024_MATRIKS_EKIVALENSI_KURIKULUM2025_KE_KURIKULUM2026.xlsx
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>`STI-305`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>K2026 memisahkan front end dan back end. `STI-312` diakui sebagai `STI-306`; mahasiswa **tetap wajib** menempuh `STI-407` Web Back End Development (3 SKS)</t>
+          <t>K2026 memisahkan front end dan back end. `STI-312` diakui sebagai `STI-311`; mahasiswa **tetap wajib** menempuh `STI-416` Web Back End Development (3 SKS)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-415`</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>`STI-304`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>`STI-602`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>**Dihapus** dari K2026 (bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016). Unsur ekstraksi fitur sinyal terserap parsial pada `STI-501` Deep Learning &amp; `STA-06` Smart Surveillance. Diakui sebagai kredit bebas 3 SKS</t>
+          <t>**Dihapus** dari K2026 (bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016). Unsur ekstraksi fitur sinyal terserap parsial pada `STI-519` Deep Learning &amp; `STA-06` Smart Surveillance. Diakui sebagai kredit bebas 3 SKS</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -5764,7 +5764,7 @@
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -5860,7 +5860,7 @@
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>`STI-304`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -5892,7 +5892,7 @@
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>`STI-305`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -5924,7 +5924,7 @@
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -5956,7 +5956,7 @@
     <row r="169" ht="16" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="173" ht="16" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -6065,7 +6065,7 @@
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-415`</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -6097,7 +6097,7 @@
     <row r="175" ht="16" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -6129,7 +6129,7 @@
     <row r="176" ht="16" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -6161,7 +6161,7 @@
     <row r="177" ht="16" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -6193,7 +6193,7 @@
     <row r="178" ht="16" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -6322,7 +6322,7 @@
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 5 — Diakui 18 SKS Paket + 3 SKS Elektif, Defisit 0 SKS Paket ✅</t>
+          <t>SEMESTER 5 — Diakui 15 SKS Paket + 3 SKS Elektif, Defisit 3 SKS Paket</t>
         </is>
       </c>
       <c r="B183" s="4" t="n"/>
@@ -6366,12 +6366,12 @@
     <row r="185" ht="16" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; Neural Networks (+P)</t>
+          <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
@@ -6381,24 +6381,24 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>**B**</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>`STI-634`</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>**Uji penyetaraan** (CNN &amp; pelatihan model)</t>
+          <t>**WAJIB TEMPUH** — jenjang keamanan lanjut</t>
         </is>
       </c>
     </row>
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -6430,7 +6430,7 @@
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
@@ -6462,7 +6462,7 @@
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -6494,7 +6494,7 @@
     <row r="189" ht="16" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -6623,7 +6623,7 @@
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>SEMESTER 6 — Diakui 10 SKS Paket + 6 SKS Elektif, Defisit 3 SKS Paket</t>
+          <t>SEMESTER 6 — Diakui 13 SKS Paket + 6 SKS Elektif, Defisit 0 SKS Paket ✅</t>
         </is>
       </c>
       <c r="B194" s="4" t="n"/>
@@ -6667,7 +6667,7 @@
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -6699,7 +6699,7 @@
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>`STI-602`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -6731,12 +6731,12 @@
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
         <is>
-          <t>Keamanan Informasi Lanjut</t>
+          <t>Deep Learning &amp; Neural Networks (+P)</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
@@ -6746,24 +6746,24 @@
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>**B**</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-634`</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>**WAJIB TEMPUH** — jenjang keamanan lanjut</t>
+          <t>**Uji penyetaraan** (CNN &amp; pelatihan model)</t>
         </is>
       </c>
     </row>
     <row r="199" ht="16" customHeight="1">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -6904,7 +6904,7 @@
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
@@ -7324,22 +7324,22 @@
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>**100%**</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -7356,22 +7356,22 @@
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>**100%**</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>`STI-201` Matematika Diskrit dan Logika</t>
+          <t>`STI-204` Matematika Diskrit dan Logika</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>`STI-503` Data Mining &amp; Visualisasi Data</t>
+          <t>`STI-520` Data Mining &amp; Visualisasi Data</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>Visualisasi tanpa didahului penambangan data menyebabkan MK Sem 2 mengajarkan alat tanpa substansi analitik. Digabung pada Sem 5 setelah `STI-401` Machine Learning</t>
+          <t>Visualisasi tanpa didahului penambangan data menyebabkan MK Sem 2 mengajarkan alat tanpa substansi analitik. Digabung pada Sem 5 setelah `STI-413` Machine Learning</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>`STI-303` UI/UX Design &amp; Prototyping</t>
+          <t>`STI-308` UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
       <c r="E231" s="7" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G233" s="7" t="inlineStr">
         <is>
-          <t>Efisiensi 7 SKS direalokasi ke `STI-103` Arsitektur STI, `STI-307` Jaringan Komputer, dan `FST-204` Pengantar AI &amp; Data</t>
+          <t>Efisiensi 7 SKS direalokasi ke `STI-103` Arsitektur STI, `STI-312` Jaringan Komputer, dan `FST-204` Pengantar AI &amp; Data</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="G245" s="9" t="inlineStr">
         <is>
-          <t>Logika Informatika K2025 dipetakan ke `STI-201` (klaster G-1). `STI-103` K2026 adalah **MK baru** yang wajib ditempuh</t>
+          <t>Logika Informatika K2025 dipetakan ke `STI-204` (klaster G-1). `STI-103` K2026 adalah **MK baru** yang wajib ditempuh</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
     <row r="247" ht="16" customHeight="1">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>`STI-405`/`STI-313`</t>
+          <t>`STI-418`/`STI-313`</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Dasar Keamanan Informasi (`STI-405`)</t>
+          <t>Dasar Keamanan Informasi (`STI-418`)</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="G251" s="7" t="inlineStr">
         <is>
-          <t>**Gap fondasi kritis K2025.** K2025 tidak mengajarkan organisasi komputer, hierarki memori, maupun representasi data tingkat mesin (BK-IS03 / BK-IT05). Menjadi prasyarat `STI-305` Sistem Operasi dan `STI-307` Jaringan Komputer</t>
+          <t>**Gap fondasi kritis K2025.** K2025 tidak mengajarkan organisasi komputer, hierarki memori, maupun representasi data tingkat mesin (BK-IS03 / BK-IT05). Menjadi prasyarat `STI-310` Sistem Operasi dan `STI-312` Jaringan Komputer</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B252" s="9" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="C252" s="9" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="G252" s="9" t="inlineStr">
         <is>
-          <t>**Gap fondasi kritis K2025.** K2025 melompat langsung ke `STI-529` Keamanan Jaringan tanpa MK jaringan komputer dasar. Prasyarat wajib bagi Cloud (`STI-404`), IoT (`STI-504`), dan Keamanan (`STI-405`)</t>
+          <t>**Gap fondasi kritis K2025.** K2025 melompat langsung ke `STI-529` Keamanan Jaringan tanpa MK jaringan komputer dasar. Prasyarat wajib bagi Cloud (`STI-417`), IoT (`STI-521`), dan Keamanan (`STI-418`)</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="B253" s="7" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E280" s="7" t="inlineStr">
         <is>
-          <t>`STI-103` (3), `STI-307` (3), `STI-603` (3)</t>
+          <t>`STI-103` (3), `STI-312` (3), `STI-519` (3)</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="D298" s="7" t="inlineStr">
         <is>
-          <t>`STI-103` (3), `FST-204` (2), `STI-307` (3)</t>
+          <t>`STI-103` (3), `FST-204` (2), `STI-312` (3)</t>
         </is>
       </c>
       <c r="E298" s="7" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>`STI-103` (3), `STI-307` (3), `FST-204` (2), `FST-610` (3)</t>
+          <t>`STI-103` (3), `STI-312` (3), `FST-204` (2), `FST-610` (3)</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>**Migrasi selektif.** `STI-103` dan `STI-307` wajib pada Sem 5 karena menjadi prasyarat Cloud, IoT, dan Keamanan; `FST-610` Capstone pada Sem 7</t>
+          <t>**Migrasi selektif.** `STI-103` dan `STI-312` wajib pada Sem 5 karena menjadi prasyarat Cloud, IoT, dan Keamanan; `FST-610` Capstone pada Sem 7</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D300" s="7" t="inlineStr">
         <is>
-          <t>`FST-610` (3) dan `STI-603` (3) atau ekuivalen</t>
+          <t>`FST-610` (3) dan `STI-519` (3) atau ekuivalen</t>
         </is>
       </c>
       <c r="E300" s="7" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="C331" s="9" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="D331" s="10" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C332" s="7" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="D332" s="8" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C336" s="7" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="D336" s="8" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="C337" s="9" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="D337" s="10" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="C338" s="7" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="D338" s="8" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="C339" s="9" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="D339" s="10" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="C340" s="7" t="inlineStr">
         <is>
-          <t>`STI-305`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="D340" s="8" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="C341" s="9" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="D341" s="10" t="inlineStr">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="C342" s="7" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="D342" s="8" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C343" s="9" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="D343" s="10" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C344" s="7" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="D344" s="8" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C349" s="9" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="D349" s="10" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="C350" s="7" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="D350" s="8" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="C351" s="9" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="D351" s="10" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="C352" s="7" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="D352" s="8" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="C353" s="9" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="D353" s="10" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="C356" s="7" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
       <c r="D356" s="8" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="C357" s="9" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="D357" s="10" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="C358" s="7" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="D358" s="8" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="C359" s="9" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="D359" s="10" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="C361" s="9" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-415`</t>
         </is>
       </c>
       <c r="D361" s="10" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="C362" s="7" t="inlineStr">
         <is>
-          <t>`STI-304`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="D362" s="8" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="C364" s="7" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="D364" s="8" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="C365" s="9" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
       <c r="D365" s="10" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>`STI-602`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="D366" s="8" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="D368" s="8" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="C369" s="9" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="D369" s="10" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="C370" s="7" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="D370" s="8" t="inlineStr">

--- a/KURIKULUM2026_REVISI/024_MATRIKS_EKIVALENSI_KURIKULUM2025_KE_KURIKULUM2026.xlsx
+++ b/KURIKULUM2026_REVISI/024_MATRIKS_EKIVALENSI_KURIKULUM2025_KE_KURIKULUM2026.xlsx
@@ -4003,7 +4003,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>`STI-519`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>**Dihapus** dari K2026 (bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016). Unsur ekstraksi fitur sinyal terserap parsial pada `STI-519` Deep Learning &amp; `STA-06` Smart Surveillance. Diakui sebagai kredit bebas 3 SKS</t>
+          <t>**Dihapus** dari K2026 (bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016). Unsur ekstraksi fitur sinyal terserap parsial pada `STI-626` Deep Learning &amp; `STA-06` Smart Surveillance. Diakui sebagai kredit bebas 3 SKS</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="B253" s="7" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F253" s="7" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="G253" s="7" t="inlineStr">
         <is>
-          <t>Penguatan jenjang keamanan bertingkat (dasar Sem 4 → lanjut Sem 6) untuk memenuhi CPL KK4 (audit, GRC &amp; tata kelola TI) pada jalur wajib, tidak hanya elektif</t>
+          <t>Penguatan jenjang keamanan bertingkat (dasar Sem 4 → lanjut Sem 5) untuk memenuhi CPL KK4 (audit, GRC &amp; tata kelola TI) pada jalur wajib, tidak hanya elektif</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/024_MATRIKS_EKIVALENSI_KURIKULUM2025_KE_KURIKULUM2026.xlsx
+++ b/KURIKULUM2026_REVISI/024_MATRIKS_EKIVALENSI_KURIKULUM2025_KE_KURIKULUM2026.xlsx
@@ -2652,7 +2652,7 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>`STC-04`</t>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>`STA-02`</t>
+          <t>`STA-601`</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>**Dihapus** dari K2026 (di luar positioning "Integrator AI"). Unsur gamifikasi terserap parsial pada `STC-01` UX Research &amp; `STC-04` XR. Diakui sebagai kredit bebas 3 SKS</t>
+          <t>**Dihapus** dari K2026 (di luar positioning "Integrator AI"). Unsur gamifikasi terserap parsial pada `STC-501` UX Research &amp; `STC-701` XR. Diakui sebagai kredit bebas 3 SKS</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>`STB-01`</t>
+          <t>`STB-501`</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>`STC-04`</t>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>`STA-01`</t>
+          <t>`STA-501`</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>**Dihapus** dari K2026 (bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016). Unsur ekstraksi fitur sinyal terserap parsial pada `STI-626` Deep Learning &amp; `STA-06` Smart Surveillance. Diakui sebagai kredit bebas 3 SKS</t>
+          <t>**Dihapus** dari K2026 (bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016). Unsur ekstraksi fitur sinyal terserap parsial pada `STI-626` Deep Learning &amp; `STA-703` Smart Surveillance. Diakui sebagai kredit bebas 3 SKS</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>`STB-04`</t>
+          <t>`STB-701`</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="G231" s="7" t="inlineStr">
         <is>
-          <t>Dua MK mengampu BK yang sama (BK-IS13 / BK-IT09) dengan overlap ± 70%. Materi riset pengguna lanjutan dipindahkan ke elektif `STC-01` UX Research &amp; Design</t>
+          <t>Dua MK mengampu BK yang sama (BK-IS13 / BK-IT09) dengan overlap ± 70%. Materi riset pengguna lanjutan dipindahkan ke elektif `STC-501` UX Research &amp; Design</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>`STC-04` Immersive Media &amp; XR Development</t>
+          <t>`STC-701` Immersive Media &amp; XR Development</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="B260" s="7" t="inlineStr">
         <is>
-          <t>`STA-03` Intelligent Agent Systems, `STA-04` MLOps and AI Pipeline, `STA-05` Conversational AI &amp; Intelligent Assistant, `STA-06` Smart Surveillance &amp; IoT Analytics</t>
+          <t>`STA-602` Intelligent Agent Systems, `STA-701` MLOps and AI Pipeline, `STA-702` Conversational AI &amp; Intelligent Assistant, `STA-703` Smart Surveillance &amp; IoT Analytics</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="D260" s="7" t="inlineStr">
         <is>
-          <t>`STA-01` ← `STI-633` SPK; `STA-02` ← `STI-317` Metode Komputasi (E2)</t>
+          <t>`STA-501` ← `STI-633` SPK; `STA-601` ← `STI-317` Metode Komputasi (E2)</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>`STB-02` Cloud Architecture &amp; DevOps, `STB-03` Cybersecurity Risk Management, `STB-05` IT Service Management ITIL 4, `STB-06` Enterprise Architecture TOGAF</t>
+          <t>`STB-601` Cloud Architecture &amp; DevOps, `STB-602` Cybersecurity Risk Management, `STB-702` IT Service Management ITIL 4, `STB-703` Enterprise Architecture TOGAF</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>`STB-01` ← `STI-529` Keamanan Jaringan; `STB-04` ← `STI-743` Audit &amp; Tata Kelola SI</t>
+          <t>`STB-501` ← `STI-529` Keamanan Jaringan; `STB-701` ← `STI-743` Audit &amp; Tata Kelola SI</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="B262" s="7" t="inlineStr">
         <is>
-          <t>`STC-01` UX Research &amp; Design, `STC-02` Rekayasa &amp; Otomasi Proses Bisnis, `STC-03` Rekayasa Aplikasi Industri Vertikal, `STC-05` SaaS Architecture &amp; Multi-Tenancy, `STC-06` Digital Product Management &amp; Agile</t>
+          <t>`STC-501` UX Research &amp; Design, `STC-601` Rekayasa &amp; Otomasi Proses Bisnis, `STC-602` Rekayasa Aplikasi Industri Vertikal, `STC-702` SaaS Architecture &amp; Multi-Tenancy, `STC-703` Digital Product Management &amp; Agile</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D262" s="7" t="inlineStr">
         <is>
-          <t>`STC-04` ← `STI-316` + `STI-531` (klaster G-4)</t>
+          <t>`STC-701` ← `STI-316` + `STI-531` (klaster G-4)</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="B267" s="7" t="inlineStr">
         <is>
-          <t>`STA-01` Decision Support Systems</t>
+          <t>`STA-501` Decision Support Systems</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="D267" s="7" t="inlineStr">
         <is>
-          <t>`STB-01` Network Security &amp; Digital Forensics</t>
+          <t>`STB-501` Network Security &amp; Digital Forensics</t>
         </is>
       </c>
       <c r="E267" s="7" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="F267" s="7" t="inlineStr">
         <is>
-          <t>`STC-01` UX Research &amp; Design</t>
+          <t>`STC-501` UX Research &amp; Design</t>
         </is>
       </c>
       <c r="G267" s="7" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="B268" s="9" t="inlineStr">
         <is>
-          <t>`STA-02` Computational Methods &amp; Numerics</t>
+          <t>`STA-601` Computational Methods &amp; Numerics</t>
         </is>
       </c>
       <c r="C268" s="9" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>`STB-02` Cloud Architecture &amp; DevOps</t>
+          <t>`STB-601` Cloud Architecture &amp; DevOps</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>`STC-02` Rekayasa &amp; Otomasi Proses Bisnis</t>
+          <t>`STC-601` Rekayasa &amp; Otomasi Proses Bisnis</t>
         </is>
       </c>
       <c r="G268" s="9" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="B269" s="7" t="inlineStr">
         <is>
-          <t>`STA-03` Intelligent Agent Systems</t>
+          <t>`STA-602` Intelligent Agent Systems</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D269" s="7" t="inlineStr">
         <is>
-          <t>`STB-03` Cybersecurity Risk Management</t>
+          <t>`STB-602` Cybersecurity Risk Management</t>
         </is>
       </c>
       <c r="E269" s="7" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="F269" s="7" t="inlineStr">
         <is>
-          <t>`STC-03` Rekayasa Aplikasi Industri Vertikal</t>
+          <t>`STC-602` Rekayasa Aplikasi Industri Vertikal</t>
         </is>
       </c>
       <c r="G269" s="7" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="B270" s="9" t="inlineStr">
         <is>
-          <t>`STA-04` MLOps and AI Pipeline</t>
+          <t>`STA-701` MLOps and AI Pipeline</t>
         </is>
       </c>
       <c r="C270" s="9" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>`STB-04` IT Governance &amp; Compliance COBIT 2019</t>
+          <t>`STB-701` IT Governance &amp; Compliance COBIT 2019</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>`STC-04` Immersive Media &amp; XR Development</t>
+          <t>`STC-701` Immersive Media &amp; XR Development</t>
         </is>
       </c>
       <c r="G270" s="9" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B271" s="7" t="inlineStr">
         <is>
-          <t>`STA-05` Conversational AI &amp; Assistant</t>
+          <t>`STA-702` Conversational AI &amp; Assistant</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="D271" s="7" t="inlineStr">
         <is>
-          <t>`STB-05` IT Service Management ITIL 4</t>
+          <t>`STB-702` IT Service Management ITIL 4</t>
         </is>
       </c>
       <c r="E271" s="7" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="F271" s="7" t="inlineStr">
         <is>
-          <t>`STC-05` SaaS Architecture &amp; Multi-Tenancy</t>
+          <t>`STC-702` SaaS Architecture &amp; Multi-Tenancy</t>
         </is>
       </c>
       <c r="G271" s="7" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="B272" s="9" t="inlineStr">
         <is>
-          <t>`STA-06` Smart Surveillance &amp; IoT Analytics</t>
+          <t>`STA-703` Smart Surveillance &amp; IoT Analytics</t>
         </is>
       </c>
       <c r="C272" s="9" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>`STB-06` Enterprise Architecture TOGAF</t>
+          <t>`STB-703` Enterprise Architecture TOGAF</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>`STC-06` Digital Product Management &amp; Agile</t>
+          <t>`STC-703` Digital Product Management &amp; Agile</t>
         </is>
       </c>
       <c r="G272" s="9" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>`STA-03`, `STA-04`, `STA-05`, `STA-06`</t>
+          <t>`STA-602`, `STA-701`, `STA-702`, `STA-703`</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="E282" s="7" t="inlineStr">
         <is>
-          <t>`STB-02`, `STB-03`, `STB-05`, `STB-06`</t>
+          <t>`STB-601`, `STB-602`, `STB-702`, `STB-703`</t>
         </is>
       </c>
     </row>
@@ -8945,7 +8945,7 @@
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>`STC-01`, `STC-02`, `STC-03`, `STC-05`, `STC-06`</t>
+          <t>`STC-501`, `STC-601`, `STC-602`, `STC-702`, `STC-703`</t>
         </is>
       </c>
     </row>
@@ -10691,9 +10691,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C346" s="8" t="inlineStr">
-        <is>
-          <t>`STC-04`</t>
+      <c r="C346" s="7" t="inlineStr">
+        <is>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="D346" s="8" t="inlineStr">
@@ -10728,9 +10728,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C347" s="10" t="inlineStr">
-        <is>
-          <t>`STC-04`</t>
+      <c r="C347" s="9" t="inlineStr">
+        <is>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="D347" s="10" t="inlineStr">
@@ -10765,9 +10765,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C348" s="8" t="inlineStr">
-        <is>
-          <t>`STA-02`</t>
+      <c r="C348" s="7" t="inlineStr">
+        <is>
+          <t>`STA-601`</t>
         </is>
       </c>
       <c r="D348" s="8" t="inlineStr">
@@ -11209,9 +11209,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C360" s="8" t="inlineStr">
-        <is>
-          <t>`STB-01`</t>
+      <c r="C360" s="7" t="inlineStr">
+        <is>
+          <t>`STB-501`</t>
         </is>
       </c>
       <c r="D360" s="8" t="inlineStr">
@@ -11320,9 +11320,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C363" s="10" t="inlineStr">
-        <is>
-          <t>`STA-01`</t>
+      <c r="C363" s="9" t="inlineStr">
+        <is>
+          <t>`STA-501`</t>
         </is>
       </c>
       <c r="D363" s="10" t="inlineStr">
@@ -11616,9 +11616,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C371" s="10" t="inlineStr">
-        <is>
-          <t>`STB-04`</t>
+      <c r="C371" s="9" t="inlineStr">
+        <is>
+          <t>`STB-701`</t>
         </is>
       </c>
       <c r="D371" s="10" t="inlineStr">
@@ -11747,9 +11747,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C376" s="8" t="inlineStr">
-        <is>
-          <t>`STA-01`</t>
+      <c r="C376" s="7" t="inlineStr">
+        <is>
+          <t>`STA-501`</t>
         </is>
       </c>
       <c r="D376" s="8" t="inlineStr">
@@ -11789,9 +11789,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C377" s="10" t="inlineStr">
-        <is>
-          <t>`STA-02`</t>
+      <c r="C377" s="9" t="inlineStr">
+        <is>
+          <t>`STA-601`</t>
         </is>
       </c>
       <c r="D377" s="10" t="inlineStr">
@@ -11831,9 +11831,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C378" s="8" t="inlineStr">
-        <is>
-          <t>`STB-01`</t>
+      <c r="C378" s="7" t="inlineStr">
+        <is>
+          <t>`STB-501`</t>
         </is>
       </c>
       <c r="D378" s="8" t="inlineStr">
@@ -11873,9 +11873,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C379" s="10" t="inlineStr">
-        <is>
-          <t>`STB-04`</t>
+      <c r="C379" s="9" t="inlineStr">
+        <is>
+          <t>`STB-701`</t>
         </is>
       </c>
       <c r="D379" s="10" t="inlineStr">
@@ -11915,9 +11915,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C380" s="8" t="inlineStr">
-        <is>
-          <t>`STC-04`</t>
+      <c r="C380" s="7" t="inlineStr">
+        <is>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="D380" s="8" t="inlineStr">
@@ -11957,9 +11957,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C381" s="10" t="inlineStr">
-        <is>
-          <t>`STC-04`</t>
+      <c r="C381" s="9" t="inlineStr">
+        <is>
+          <t>`STC-701`</t>
         </is>
       </c>
       <c r="D381" s="10" t="inlineStr">
